--- a/sample_data/TGFbeta_sample.xlsx
+++ b/sample_data/TGFbeta_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,13 +463,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.99850892478008</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>6.669787469258273</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -486,20 +486,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EEA1</t>
+          <t>Cav1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.66118071562891</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>12.48204463755737</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
+        <v>301</v>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.69412317831902</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>20.05004713656291</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
+        <v>301</v>
+      </c>
+      <c r="F4" t="n">
         <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -540,20 +540,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EEA1</t>
+          <t>Cav1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.09181334692855</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>13.98877591977703</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
+        <v>301</v>
+      </c>
+      <c r="F5" t="n">
         <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -571,16 +571,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24.6766982417311</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>17.2663204709568</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
+        <v>301</v>
+      </c>
+      <c r="F6" t="n">
         <v>5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -594,20 +594,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EEA1</t>
+          <t>Cav1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.145289250490411</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>14.07403747954929</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
+        <v>301</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.55309885045872</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>20.32824252808192</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
+        <v>301</v>
+      </c>
+      <c r="F8" t="n">
         <v>7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -648,20 +648,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EEA1</t>
+          <t>Cav1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.80357843956854</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>17.67504643085796</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
+        <v>301</v>
+      </c>
+      <c r="F9" t="n">
         <v>8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.028834966365</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>17.62586762322534</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
+        <v>301</v>
+      </c>
+      <c r="F10" t="n">
         <v>9</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -702,20 +702,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EEA1</t>
+          <t>Cav1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14.64206991291058</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>19.68387104876831</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
+        <v>301</v>
+      </c>
+      <c r="F11" t="n">
         <v>10</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.894810851318977</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>17.28593903273887</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
+        <v>301</v>
+      </c>
+      <c r="F12" t="n">
         <v>11</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.090853782759252</v>
+        <v>15.08</v>
       </c>
       <c r="D13" t="n">
-        <v>12.22295216596493</v>
+        <v>15.05</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>401</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -779,21 +779,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cav1</t>
+          <t>EEA1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18.29175278769368</v>
+        <v>15.08</v>
       </c>
       <c r="D14" t="n">
-        <v>11.85927405491513</v>
+        <v>15.05</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>401</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -814,16 +814,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.72978119337938</v>
+        <v>15.08</v>
       </c>
       <c r="D15" t="n">
-        <v>14.84034129530584</v>
+        <v>15.05</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -833,24 +833,24 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cav1</t>
+          <t>EEA1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.3602446666407</v>
+        <v>15.08</v>
       </c>
       <c r="D16" t="n">
-        <v>10.68045596333921</v>
+        <v>15.05</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>401</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -868,16 +868,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.29058899367396</v>
+        <v>15.08</v>
       </c>
       <c r="D17" t="n">
-        <v>22.54239807397482</v>
+        <v>15.05</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>401</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -887,24 +887,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cav1</t>
+          <t>EEA1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.641631355870351</v>
+        <v>15.08</v>
       </c>
       <c r="D18" t="n">
-        <v>13.5188590184457</v>
+        <v>15.05</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>401</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -922,16 +922,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18.41626599058361</v>
+        <v>15.08</v>
       </c>
       <c r="D19" t="n">
-        <v>7.267892364508562</v>
+        <v>15.05</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>401</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -941,24 +941,24 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cav1</t>
+          <t>EEA1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.93682585364378</v>
+        <v>15.08</v>
       </c>
       <c r="D20" t="n">
-        <v>12.70867957116444</v>
+        <v>15.05</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>401</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -976,18 +976,72 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19.77820302286997</v>
+        <v>15.08</v>
       </c>
       <c r="D21" t="n">
-        <v>5.807045621367799</v>
+        <v>15.05</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>TGFbeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EEA1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="E22" t="n">
+        <v>401</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>TGFbeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EEA1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="E23" t="n">
+        <v>401</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>TGFbeta</t>
         </is>
